--- a/output/pdf_financials_xlsx/PDQ.xlsx
+++ b/output/pdf_financials_xlsx/PDQ.xlsx
@@ -1309,40 +1309,40 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.305257</v>
+        <v>-0.305257</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.401693</v>
+        <v>-0.401693</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.913734</v>
+        <v>-0.916234</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.963569</v>
+        <v>-0.961069</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.897714</v>
+        <v>-0.897714</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.133634</v>
+        <v>-1.133634</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.274538</v>
+        <v>-0.274538</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.429013</v>
+        <v>-0.429013</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.622497</v>
+        <v>-0.622497</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.835406</v>
+        <v>-0.835406</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.299592</v>
+        <v>-0.299592</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.118971</v>
+        <v>-1.118971</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1355,13 +1355,13 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.264983</v>
+        <v>-1.264983</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1.61024</v>
+        <v>-1.61024</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.109657</v>
+        <v>-0.109657</v>
       </c>
     </row>
     <row r="17">
@@ -1617,40 +1617,40 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.305257</v>
+        <v>-0.305257</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.401693</v>
+        <v>-0.401693</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.914984</v>
+        <v>-0.914984</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.962319</v>
+        <v>-0.962319</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.897714</v>
+        <v>-0.897714</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.133634</v>
+        <v>-1.133634</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.274538</v>
+        <v>-0.274538</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.429013</v>
+        <v>-0.429013</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.622497</v>
+        <v>-0.622497</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.835406</v>
+        <v>-0.835406</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.299592</v>
+        <v>-0.299592</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.118971</v>
+        <v>-1.118971</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.264983</v>
+        <v>-1.264983</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>1.61024</v>
+        <v>-1.61024</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.109657</v>
+        <v>-0.109657</v>
       </c>
     </row>
     <row r="21">
@@ -1803,40 +1803,40 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.305257</v>
+        <v>-0.305257</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.401693</v>
+        <v>-0.401693</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.914984</v>
+        <v>-0.914984</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.962319</v>
+        <v>-0.962319</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.897714</v>
+        <v>-0.897714</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.133634</v>
+        <v>-1.133634</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.274538</v>
+        <v>-0.274538</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.429013</v>
+        <v>-0.429013</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.622497</v>
+        <v>-0.622497</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.835406</v>
+        <v>-0.835406</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.299592</v>
+        <v>-0.299592</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.118971</v>
+        <v>-1.118971</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.264983</v>
+        <v>-1.264983</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1.61024</v>
+        <v>-1.61024</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.109657</v>
+        <v>-0.109657</v>
       </c>
     </row>
     <row r="24">
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>15.26285</v>
+        <v>-15.26285</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>45.7492</v>
+        <v>-45.7492</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>8.748355</v>
+        <v>-8.748355</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>11.221425</v>
+        <v>-11.221425</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>28.34085</v>
+        <v>-28.34085</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>31.12485</v>
+        <v>-31.12485</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>7.4898</v>
+        <v>-7.4898</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8.607469</v>
+        <v>-8.607469</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>9.035593</v>
+        <v>-9.035593</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>8.945778000000001</v>
+        <v>-8.945778000000001</v>
       </c>
       <c r="R26" s="1" t="inlineStr">
         <is>
@@ -2061,40 +2061,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.305257</v>
+        <v>-0.305257</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.401693</v>
+        <v>-0.401693</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.913734</v>
+        <v>-0.916234</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.963569</v>
+        <v>-0.961069</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.897714</v>
+        <v>-0.897714</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.133634</v>
+        <v>-1.133634</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.274538</v>
+        <v>-0.274538</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.429013</v>
+        <v>-0.429013</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.622497</v>
+        <v>-0.622497</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.835406</v>
+        <v>-0.835406</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.299592</v>
+        <v>-0.299592</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.118971</v>
+        <v>-1.118971</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.264983</v>
+        <v>-1.264983</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>1.61024</v>
+        <v>-1.61024</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.109657</v>
+        <v>-0.109657</v>
       </c>
     </row>
     <row r="28">
@@ -2185,40 +2185,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.305257</v>
+        <v>-0.305257</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.401693</v>
+        <v>-0.401693</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.913734</v>
+        <v>-0.916234</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.963569</v>
+        <v>-0.961069</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.897714</v>
+        <v>-0.897714</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.133634</v>
+        <v>-1.133634</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.274538</v>
+        <v>-0.274538</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.429013</v>
+        <v>-0.429013</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.622497</v>
+        <v>-0.622497</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.835406</v>
+        <v>-0.835406</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.299592</v>
+        <v>-0.299592</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.118971</v>
+        <v>-1.118971</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.264983</v>
+        <v>-1.264983</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>1.61024</v>
+        <v>-1.61024</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.109657</v>
+        <v>-0.109657</v>
       </c>
     </row>
     <row r="30">
@@ -2339,40 +2339,40 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.1368013010350934</v>
+        <v>-0.1364280303939823</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.1297260497172491</v>
+        <v>-0.1300635022043162</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
@@ -2385,13 +2385,13 @@
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5970,49 +5970,49 @@
         <v>0.53259</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.549943</v>
+        <v>0.462129</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.440932</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.537353</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.443605</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.240708</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.237867</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.427164</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.428898</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.502008</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.503003</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.886437</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.6774790000000001</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.720736</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.634276</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.049869</v>
       </c>
     </row>
     <row r="93">
@@ -6593,25 +6593,25 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.000586</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.007236</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.012209</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.005961</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.047265</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.047197</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.005716</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>0.002681</v>
@@ -9835,7 +9835,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10932,7 +10936,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11031,7 +11039,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -12423,7 +12435,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -12518,7 +12534,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13185,7 +13205,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13680,7 +13704,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -13771,7 +13799,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -15937,7 +15969,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -16034,7 +16070,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -16729,7 +16769,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.009317000000000001</v>
       </c>
@@ -17525,7 +17569,11 @@
           <t>Prepaid and deposits 9</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -17931,7 +17979,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -20145,7 +20197,11 @@
           <t>Prepaid and deposits 10</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -20549,7 +20605,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -21149,7 +21209,11 @@
           <t>Prepaid and deposits 8,329</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -22064,7 +22128,11 @@
           <t>Share-based payment reserve 440,932</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -33531,7 +33599,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E254" s="5" t="n">
         <v>0.000586</v>
       </c>
@@ -40777,13 +40849,13 @@
         </is>
       </c>
       <c r="S326" s="5" t="n">
-        <v>1.264983</v>
+        <v>-1.264983</v>
       </c>
       <c r="T326" s="5" t="n">
-        <v>1.61024</v>
+        <v>-1.61024</v>
       </c>
       <c r="U326" s="5" t="n">
-        <v>0.109657</v>
+        <v>-0.109657</v>
       </c>
     </row>
     <row r="327">
@@ -43217,28 +43289,28 @@
         </is>
       </c>
       <c r="I352" s="5" t="n">
-        <v>0.897714</v>
+        <v>-0.897714</v>
       </c>
       <c r="J352" s="5" t="n">
-        <v>1.133634</v>
+        <v>-1.133634</v>
       </c>
       <c r="K352" s="5" t="n">
-        <v>0.274538</v>
+        <v>-0.274538</v>
       </c>
       <c r="L352" s="5" t="n">
-        <v>0.429013</v>
+        <v>-0.429013</v>
       </c>
       <c r="M352" s="5" t="n">
-        <v>0.622497</v>
+        <v>-0.622497</v>
       </c>
       <c r="N352" s="5" t="n">
-        <v>0.835406</v>
+        <v>-0.835406</v>
       </c>
       <c r="O352" s="5" t="n">
-        <v>0.299592</v>
+        <v>-0.299592</v>
       </c>
       <c r="P352" s="5" t="n">
-        <v>1.118971</v>
+        <v>-1.118971</v>
       </c>
       <c r="Q352" t="inlineStr">
         <is>
@@ -46453,10 +46525,10 @@
         </is>
       </c>
       <c r="H385" s="5" t="n">
-        <v>0.962319</v>
+        <v>-0.962319</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>0.897714</v>
+        <v>-0.897714</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
@@ -46753,13 +46825,13 @@
         </is>
       </c>
       <c r="G388" s="5" t="n">
-        <v>0.906234</v>
+        <v>-0.906234</v>
       </c>
       <c r="H388" s="5" t="n">
-        <v>0.966069</v>
+        <v>-0.966069</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>0.897714</v>
+        <v>-0.897714</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -48054,16 +48126,16 @@
         </is>
       </c>
       <c r="E401" s="5" t="n">
-        <v>0.305257</v>
+        <v>-0.305257</v>
       </c>
       <c r="F401" s="5" t="n">
-        <v>0.401693</v>
+        <v>-0.401693</v>
       </c>
       <c r="G401" s="5" t="n">
-        <v>0.914984</v>
+        <v>-0.914984</v>
       </c>
       <c r="H401" s="5" t="n">
-        <v>0.962319</v>
+        <v>-0.962319</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -49263,10 +49335,10 @@
         </is>
       </c>
       <c r="F413" s="5" t="n">
-        <v>0.401693</v>
+        <v>-0.401693</v>
       </c>
       <c r="G413" s="5" t="n">
-        <v>0.243691</v>
+        <v>-0.243691</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
@@ -49465,10 +49537,10 @@
         </is>
       </c>
       <c r="F415" s="5" t="n">
-        <v>0.406693</v>
+        <v>-0.406693</v>
       </c>
       <c r="G415" s="5" t="n">
-        <v>0.234941</v>
+        <v>-0.234941</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PDQ.xlsx
+++ b/output/pdf_financials_xlsx/PDQ.xlsx
@@ -1067,16 +1067,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000371</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003307</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000731</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000646</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -2067,16 +2067,16 @@
         <v>-0.401693</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.916234</v>
+        <v>-0.915863</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.961069</v>
+        <v>-0.957762</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.897714</v>
+        <v>-0.896983</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.133634</v>
+        <v>-1.132988</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.274538</v>
@@ -2191,16 +2191,16 @@
         <v>-0.401693</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.916234</v>
+        <v>-0.915863</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.961069</v>
+        <v>-0.957762</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.897714</v>
+        <v>-0.896983</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.133634</v>
+        <v>-1.132988</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.274538</v>
@@ -2500,55 +2500,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.128036</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.587199</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.587199</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.161636</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.449161</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.055206</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003756</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.5341939999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.008671999999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.006661</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.009653999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.284586</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.137494</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.036979</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.003569</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.153081</v>
       </c>
     </row>
     <row r="35">
@@ -2616,55 +2616,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.128036</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.587199</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.587199</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.161636</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.449161</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.055206</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003756</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.5341939999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.008671999999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.006661</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.009653999999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.00345</v>
+        <v>0.288036</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.0022</v>
+        <v>0.139694</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.001075</v>
+        <v>0.038054</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.002</v>
+        <v>0.005569</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.001525</v>
+        <v>0.154606</v>
       </c>
     </row>
     <row r="37">
@@ -3312,55 +3312,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.137353</v>
+        <v>0.009317000000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.58928</v>
+        <v>0.002081</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.58928</v>
+        <v>0.002081</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.169965</v>
+        <v>0.008329</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.504755</v>
+        <v>0.055594</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.06360300000000001</v>
+        <v>0.008397</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.006437</v>
+        <v>0.002681</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.536979</v>
+        <v>0.002785</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.014017</v>
+        <v>0.005345</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.014526</v>
+        <v>0.007865</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.068332</v>
+        <v>0.058678</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.294647</v>
+        <v>0.010061</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.157186</v>
+        <v>0.019692</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.055555</v>
+        <v>0.018576</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.004569</v>
+        <v>0.001</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.153081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -45500,7 +45500,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -47415,7 +47415,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">

--- a/output/pdf_financials_xlsx/PDQ.xlsx
+++ b/output/pdf_financials_xlsx/PDQ.xlsx
@@ -3428,7 +3428,7 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0.02</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.003143</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -4394,7 +4394,7 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>0</v>
+        <v>0.285862</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0.463737</v>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>7.598368</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>8.458736</v>
@@ -23960,7 +23960,11 @@
           <t>Equipment Note 6</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E155" s="5" t="n">
         <v>0.003143</v>
       </c>
@@ -24061,7 +24065,11 @@
           <t>Investments Note 7</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>4e-06</v>
       </c>
@@ -24160,7 +24168,11 @@
           <t>Mineral properties Note 8</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E157" s="5" t="n">
         <v>1.978136</v>
       </c>
@@ -24259,7 +24271,11 @@
           <t>Bank indebtedness Note 9 $</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BankIndebtedness</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="n">
         <v>0.19933</v>
       </c>
@@ -24358,7 +24374,11 @@
           <t>Due to related parties Note 10</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
         <v>0.285862</v>
       </c>
@@ -24457,7 +24477,11 @@
           <t>Share capital Note 11</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
         <v>7.598368</v>
       </c>

--- a/output/pdf_financials_xlsx/PDQ.xlsx
+++ b/output/pdf_financials_xlsx/PDQ.xlsx
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.07964300000000001</v>
+        <v>0.123227</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.09238</v>
+        <v>0.142381</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.081438</v>
+        <v>0.104688</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.087725</v>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.305257</v>
+        <v>0.288698</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.401693</v>
+        <v>0.25</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.916234</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.593955</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.651693</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>0.00125</v>
@@ -1838,15 +1838,11 @@
       <c r="M23" s="3" t="n">
         <v>-1.118971</v>
       </c>
-      <c r="N23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N23" s="3" t="n">
+        <v>-1.133763</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0.001767</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-1.264983</v>
@@ -2061,10 +2057,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.305257</v>
+        <v>0.288698</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.401693</v>
+        <v>0.25</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.915863</v>
@@ -2185,10 +2181,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.305257</v>
+        <v>0.288698</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.401693</v>
+        <v>0.25</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.915863</v>
@@ -2339,10 +2335,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>205.7357515465989</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>260.6772</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0.1364280303939823</v>
@@ -6392,15 +6388,11 @@
       <c r="M99" s="3" t="n">
         <v>-1.118971</v>
       </c>
-      <c r="N99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N99" s="3" t="n">
+        <v>-1.133763</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>0.001767</v>
       </c>
       <c r="P99" s="3" t="n">
         <v>-1.264983</v>
@@ -26582,7 +26574,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -28006,7 +28002,11 @@
           <t>Net Income (Loss)</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -28586,7 +28586,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -29384,7 +29388,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -32441,7 +32449,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -34403,7 +34415,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -34605,7 +34621,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -34904,7 +34924,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -35510,7 +35534,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E273" s="5" t="n">
         <v>-0.288698</v>
       </c>
@@ -47235,7 +47263,11 @@
           <t>Independent directors' fees</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -48647,7 +48679,11 @@
           <t>Independent director fees</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -49150,7 +49186,11 @@
           <t>Loss Before Future Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -49249,7 +49289,11 @@
           <t>Future income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -50263,7 +50307,11 @@
           <t>Independent directors' fees</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E422" s="5" t="n">
         <v>0.043584</v>
       </c>
@@ -51887,7 +51935,11 @@
           <t>Loss Before Future Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E438" s="5" t="n">
         <v>0.593955</v>
       </c>
@@ -51986,7 +52038,11 @@
           <t>Future Income Tax Recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E439" s="5" t="n">
         <v>-0.288698</v>
       </c>
